--- a/Result/profitability/6188.xlsx
+++ b/Result/profitability/6188.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7675000000000001</v>
+        <v>0.7887500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>25.815</v>
+        <v>25.7525</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.96</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8412500000000001</v>
+        <v>0.82125</v>
       </c>
       <c r="N3" t="n">
-        <v>23.48375</v>
+        <v>23.36375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.24</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9087499999999999</v>
+        <v>0.85625</v>
       </c>
       <c r="N4" t="n">
-        <v>21.10125</v>
+        <v>20.97</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>0.77</v>
       </c>
       <c r="M5" t="n">
-        <v>0.885</v>
+        <v>0.84875</v>
       </c>
       <c r="N5" t="n">
-        <v>18.84875</v>
+        <v>18.54875</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.36</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9512499999999999</v>
+        <v>0.89625</v>
       </c>
       <c r="N6" t="n">
-        <v>16.44375</v>
+        <v>16.34875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.55</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0225</v>
+        <v>0.9850000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>14.50625</v>
+        <v>14.6525</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.36</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0875</v>
+        <v>1.09875</v>
       </c>
       <c r="N8" t="n">
-        <v>12.79375</v>
+        <v>13.23125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6188</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1965</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1415</v>
+      </c>
+      <c r="E75" t="n">
+        <v>551</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="G75" t="n">
+        <v>92</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.69%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>153</v>
+      </c>
+      <c r="J75" t="n">
+        <v>246</v>
+      </c>
+      <c r="K75" t="n">
+        <v>149</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.70875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>28.155</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.09000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1426824296779454</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.2899999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3493975903614457</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.399999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.07886953664147223</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
